--- a/artfynd/A 33477-2026 artfynd.xlsx
+++ b/artfynd/A 33477-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136125419</v>
+        <v>136193005</v>
       </c>
       <c r="B2" t="n">
-        <v>97958</v>
+        <v>96618</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2606</v>
+        <v>1080</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Björkasjö, Hl</t>
+          <t>Gräsberg, Hl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>354145</v>
+        <v>354093</v>
       </c>
       <c r="R2" t="n">
-        <v>6332000</v>
+        <v>6332012</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,27 +775,27 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Sindy Gullberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Sindy Gullberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136125419</t>
+          <t>https://artportalen.se/Sighting/136193005</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136125421</v>
+        <v>136194461</v>
       </c>
       <c r="B3" t="n">
-        <v>96597</v>
+        <v>96618</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,41 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2671</v>
+        <v>1080</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Öarna, Hl</t>
+          <t>Gräsberg, Hl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>354136</v>
+        <v>354150</v>
       </c>
       <c r="R3" t="n">
-        <v>6332022</v>
+        <v>6331973</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,22 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,34 +881,33 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Sindy Gullberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Sindy Gullberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136125421</t>
+          <t>https://artportalen.se/Sighting/136194461</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136125420</v>
+        <v>136192933</v>
       </c>
       <c r="B4" t="n">
-        <v>96402</v>
+        <v>77950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,37 +915,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2779</v>
+        <v>1095</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Mussellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Normandina pulchella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Borrer) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Björkasjö, Hl</t>
+          <t>Gräsberg, Hl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>354139</v>
+        <v>354093</v>
       </c>
       <c r="R4" t="n">
-        <v>6332023</v>
+        <v>6332012</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,22 +969,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,65 +999,65 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Sindy Gullberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Sindy Gullberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136125420</t>
+          <t>https://artportalen.se/Sighting/136192933</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136125414</v>
+        <v>136193523</v>
       </c>
       <c r="B5" t="n">
-        <v>58141</v>
+        <v>81120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103020</v>
+        <v>1144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Björkasjö, Hl</t>
+          <t>Gräsberg, Hl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>354164</v>
+        <v>354093</v>
       </c>
       <c r="R5" t="n">
-        <v>6332055</v>
+        <v>6332012</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,22 +1081,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,65 +1111,65 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Sindy Gullberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Sindy Gullberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136125414</t>
+          <t>https://artportalen.se/Sighting/136193523</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136125410</v>
+        <v>136194440</v>
       </c>
       <c r="B6" t="n">
-        <v>58138</v>
+        <v>77839</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103023</v>
+        <v>1342</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Björkasjö, Hl</t>
+          <t>Gräsberg, Hl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>354125</v>
+        <v>354177</v>
       </c>
       <c r="R6" t="n">
-        <v>6332040</v>
+        <v>6331979</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,22 +1193,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,18 +1223,1479 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Sindy Gullberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Sindy Gullberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136194440</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136125419</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97958</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2606</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Klippfrullania</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Frullania tamarisci</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Björkasjö, Hl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>354145</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6332000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Köinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136125419</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136193996</v>
+      </c>
+      <c r="B8" t="n">
+        <v>96608</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gräsberg, Hl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>354172</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6332026</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Köinge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136193996</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136125421</v>
+      </c>
+      <c r="B9" t="n">
+        <v>96597</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Öarna, Hl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>354136</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6332022</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Köinge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136125421</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136193735</v>
+      </c>
+      <c r="B10" t="n">
+        <v>96597</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gräsberg, Hl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>354093</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6332012</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Köinge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136193735</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136193984</v>
+      </c>
+      <c r="B11" t="n">
+        <v>96597</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gräsberg, Hl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>354172</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6332026</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Köinge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136193984</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136125420</v>
+      </c>
+      <c r="B12" t="n">
+        <v>96402</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Björkasjö, Hl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>354139</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6332023</v>
+      </c>
+      <c r="S12" t="n">
+        <v>11</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Köinge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136125420</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136193836</v>
+      </c>
+      <c r="B13" t="n">
+        <v>96402</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gräsberg, Hl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>354093</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6332012</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Köinge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136193836</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136194444</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79700</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6459</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Barkkornlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lopadium disciforme</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Gräsberg, Hl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>354177</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6331979</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Köinge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136194444</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136125414</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Björkasjö, Hl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>354164</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6332055</v>
+      </c>
+      <c r="S15" t="n">
+        <v>8</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Köinge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136125414</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136125410</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58138</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Björkasjö, Hl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>354125</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6332040</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Köinge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/136125410</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136192690</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98148</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>224361</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gräsberg, Hl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>354051</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6331948</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Köinge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136192690</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136192731</v>
+      </c>
+      <c r="B18" t="n">
+        <v>81107</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Gräsberg, Hl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>354051</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6331948</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Köinge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136192731</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136192963</v>
+      </c>
+      <c r="B19" t="n">
+        <v>81107</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Gräsberg, Hl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>354093</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6332012</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Köinge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136192963</t>
         </is>
       </c>
     </row>
@@ -1250,6 +2706,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33477-2026 artfynd.xlsx
+++ b/artfynd/A 33477-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193005</v>
       </c>
       <c r="B2" t="n">
-        <v>96618</v>
+        <v>96619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136194461</v>
       </c>
       <c r="B3" t="n">
-        <v>96618</v>
+        <v>96619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136125419</v>
       </c>
       <c r="B7" t="n">
-        <v>97958</v>
+        <v>97959</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136193996</v>
       </c>
       <c r="B8" t="n">
-        <v>96608</v>
+        <v>96609</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136125421</v>
       </c>
       <c r="B9" t="n">
-        <v>96597</v>
+        <v>96598</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>136193735</v>
       </c>
       <c r="B10" t="n">
-        <v>96597</v>
+        <v>96598</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>136193984</v>
       </c>
       <c r="B11" t="n">
-        <v>96597</v>
+        <v>96598</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136125420</v>
       </c>
       <c r="B12" t="n">
-        <v>96402</v>
+        <v>96403</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136193836</v>
       </c>
       <c r="B13" t="n">
-        <v>96402</v>
+        <v>96403</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>136192690</v>
       </c>
       <c r="B17" t="n">
-        <v>98148</v>
+        <v>98149</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 33477-2026 artfynd.xlsx
+++ b/artfynd/A 33477-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193005</v>
       </c>
       <c r="B2" t="n">
-        <v>96619</v>
+        <v>96620</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136194461</v>
       </c>
       <c r="B3" t="n">
-        <v>96619</v>
+        <v>96620</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136192933</v>
       </c>
       <c r="B4" t="n">
-        <v>77950</v>
+        <v>77951</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136193523</v>
       </c>
       <c r="B5" t="n">
-        <v>81120</v>
+        <v>81121</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136194440</v>
       </c>
       <c r="B6" t="n">
-        <v>77839</v>
+        <v>77840</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136125419</v>
       </c>
       <c r="B7" t="n">
-        <v>97959</v>
+        <v>97960</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136193996</v>
       </c>
       <c r="B8" t="n">
-        <v>96609</v>
+        <v>96610</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136125421</v>
       </c>
       <c r="B9" t="n">
-        <v>96598</v>
+        <v>96599</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>136193735</v>
       </c>
       <c r="B10" t="n">
-        <v>96598</v>
+        <v>96599</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>136193984</v>
       </c>
       <c r="B11" t="n">
-        <v>96598</v>
+        <v>96599</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136125420</v>
       </c>
       <c r="B12" t="n">
-        <v>96403</v>
+        <v>96404</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136193836</v>
       </c>
       <c r="B13" t="n">
-        <v>96403</v>
+        <v>96404</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>136194444</v>
       </c>
       <c r="B14" t="n">
-        <v>79700</v>
+        <v>79701</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136125414</v>
       </c>
       <c r="B15" t="n">
-        <v>58141</v>
+        <v>58142</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136125410</v>
       </c>
       <c r="B16" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>136192690</v>
       </c>
       <c r="B17" t="n">
-        <v>98149</v>
+        <v>98150</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>136192731</v>
       </c>
       <c r="B18" t="n">
-        <v>81107</v>
+        <v>81108</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136192963</v>
       </c>
       <c r="B19" t="n">
-        <v>81107</v>
+        <v>81108</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 33477-2026 artfynd.xlsx
+++ b/artfynd/A 33477-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193005</v>
       </c>
       <c r="B2" t="n">
-        <v>96620</v>
+        <v>96626</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136194461</v>
       </c>
       <c r="B3" t="n">
-        <v>96620</v>
+        <v>96626</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136192933</v>
       </c>
       <c r="B4" t="n">
-        <v>77951</v>
+        <v>77955</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136193523</v>
       </c>
       <c r="B5" t="n">
-        <v>81121</v>
+        <v>81125</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136194440</v>
       </c>
       <c r="B6" t="n">
-        <v>77840</v>
+        <v>77844</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136125419</v>
       </c>
       <c r="B7" t="n">
-        <v>97960</v>
+        <v>97966</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136193996</v>
       </c>
       <c r="B8" t="n">
-        <v>96610</v>
+        <v>96616</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136125421</v>
       </c>
       <c r="B9" t="n">
-        <v>96599</v>
+        <v>96605</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>136193735</v>
       </c>
       <c r="B10" t="n">
-        <v>96599</v>
+        <v>96605</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>136193984</v>
       </c>
       <c r="B11" t="n">
-        <v>96599</v>
+        <v>96605</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136125420</v>
       </c>
       <c r="B12" t="n">
-        <v>96404</v>
+        <v>96410</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136193836</v>
       </c>
       <c r="B13" t="n">
-        <v>96404</v>
+        <v>96410</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>136194444</v>
       </c>
       <c r="B14" t="n">
-        <v>79701</v>
+        <v>79705</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136125414</v>
       </c>
       <c r="B15" t="n">
-        <v>58142</v>
+        <v>58146</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136125410</v>
       </c>
       <c r="B16" t="n">
-        <v>58139</v>
+        <v>58143</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>136192690</v>
       </c>
       <c r="B17" t="n">
-        <v>98150</v>
+        <v>98156</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>136192731</v>
       </c>
       <c r="B18" t="n">
-        <v>81108</v>
+        <v>81112</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136192963</v>
       </c>
       <c r="B19" t="n">
-        <v>81108</v>
+        <v>81112</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 33477-2026 artfynd.xlsx
+++ b/artfynd/A 33477-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ19"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>136193005</v>
       </c>
       <c r="B2" t="n">
-        <v>96626</v>
+        <v>96627</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136194461</v>
       </c>
       <c r="B3" t="n">
-        <v>96626</v>
+        <v>96627</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136192933</v>
       </c>
       <c r="B4" t="n">
-        <v>77955</v>
+        <v>77956</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136193523</v>
       </c>
       <c r="B5" t="n">
-        <v>81125</v>
+        <v>81126</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136194440</v>
       </c>
       <c r="B6" t="n">
-        <v>77844</v>
+        <v>77845</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,48 +1240,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136125419</v>
+        <v>136320537</v>
       </c>
       <c r="B7" t="n">
-        <v>97966</v>
+        <v>81283</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2606</v>
+        <v>1557</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Röd pysslinglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelopsis rubella</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Björkasjö, Hl</t>
+          <t>Gräsberg, Hl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>354145</v>
+        <v>354136</v>
       </c>
       <c r="R7" t="n">
-        <v>6332000</v>
+        <v>6332045</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,22 +1305,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,27 +1335,27 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Sindy Gullberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Sindy Gullberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136125419</t>
+          <t>https://artportalen.se/Sighting/136320537</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136193996</v>
+        <v>136125419</v>
       </c>
       <c r="B8" t="n">
-        <v>96616</v>
+        <v>97967</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,37 +1363,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2667</v>
+        <v>2606</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gräsberg, Hl</t>
+          <t>Björkasjö, Hl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>354172</v>
+        <v>354145</v>
       </c>
       <c r="R8" t="n">
-        <v>6332026</v>
+        <v>6332000</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1417,22 +1417,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,27 +1447,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sindy Gullberg</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sindy Gullberg</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136193996</t>
+          <t>https://artportalen.se/Sighting/136125419</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136125421</v>
+        <v>136193996</v>
       </c>
       <c r="B9" t="n">
-        <v>96605</v>
+        <v>96617</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,41 +1475,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Öarna, Hl</t>
+          <t>Gräsberg, Hl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>354136</v>
+        <v>354172</v>
       </c>
       <c r="R9" t="n">
-        <v>6332022</v>
+        <v>6332026</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1533,22 +1529,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1557,34 +1553,33 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Sindy Gullberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Sindy Gullberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136125421</t>
+          <t>https://artportalen.se/Sighting/136193996</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136193735</v>
+        <v>136125421</v>
       </c>
       <c r="B10" t="n">
-        <v>96605</v>
+        <v>96606</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,16 +1605,20 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gräsberg, Hl</t>
+          <t>Öarna, Hl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>354093</v>
+        <v>354136</v>
       </c>
       <c r="R10" t="n">
-        <v>6332012</v>
+        <v>6332022</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1646,22 +1645,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1670,33 +1669,34 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Sindy Gullberg</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sindy Gullberg</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136193735</t>
+          <t>https://artportalen.se/Sighting/136125421</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136193984</v>
+        <v>136193735</v>
       </c>
       <c r="B11" t="n">
-        <v>96605</v>
+        <v>96606</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>354172</v>
+        <v>354093</v>
       </c>
       <c r="R11" t="n">
-        <v>6332026</v>
+        <v>6332012</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1799,16 +1799,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136193984</t>
+          <t>https://artportalen.se/Sighting/136193735</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136125420</v>
+        <v>136193984</v>
       </c>
       <c r="B12" t="n">
-        <v>96410</v>
+        <v>96606</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1816,37 +1816,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2779</v>
+        <v>2671</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Björkasjö, Hl</t>
+          <t>Gräsberg, Hl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>354139</v>
+        <v>354172</v>
       </c>
       <c r="R12" t="n">
-        <v>6332023</v>
+        <v>6332026</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1870,22 +1870,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1900,27 +1900,27 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Sindy Gullberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Sindy Gullberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136125420</t>
+          <t>https://artportalen.se/Sighting/136193984</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136193836</v>
+        <v>136125420</v>
       </c>
       <c r="B13" t="n">
-        <v>96410</v>
+        <v>96411</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1948,17 +1948,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gräsberg, Hl</t>
+          <t>Björkasjö, Hl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>354093</v>
+        <v>354139</v>
       </c>
       <c r="R13" t="n">
-        <v>6332012</v>
+        <v>6332023</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1982,22 +1982,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2012,27 +2012,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Sindy Gullberg</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Sindy Gullberg</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136193836</t>
+          <t>https://artportalen.se/Sighting/136125420</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136194444</v>
+        <v>136193836</v>
       </c>
       <c r="B14" t="n">
-        <v>79705</v>
+        <v>96411</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2040,21 +2040,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6459</v>
+        <v>2779</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2064,13 +2064,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>354177</v>
+        <v>354093</v>
       </c>
       <c r="R14" t="n">
-        <v>6331979</v>
+        <v>6332012</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2135,54 +2135,54 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136194444</t>
+          <t>https://artportalen.se/Sighting/136193836</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136125414</v>
+        <v>136194444</v>
       </c>
       <c r="B15" t="n">
-        <v>58146</v>
+        <v>79706</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103020</v>
+        <v>6459</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Björkasjö, Hl</t>
+          <t>Gräsberg, Hl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>354164</v>
+        <v>354177</v>
       </c>
       <c r="R15" t="n">
-        <v>6332055</v>
+        <v>6331979</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2206,22 +2206,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2236,44 +2236,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Sindy Gullberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Sindy Gullberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136125414</t>
+          <t>https://artportalen.se/Sighting/136194444</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136125410</v>
+        <v>136125414</v>
       </c>
       <c r="B16" t="n">
-        <v>58143</v>
+        <v>58147</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103023</v>
+        <v>103020</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2288,13 +2288,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>354125</v>
+        <v>354164</v>
       </c>
       <c r="R16" t="n">
-        <v>6332040</v>
+        <v>6332055</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2359,16 +2359,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136125410</t>
+          <t>https://artportalen.se/Sighting/136125414</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136192690</v>
+        <v>136125410</v>
       </c>
       <c r="B17" t="n">
-        <v>98156</v>
+        <v>58144</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2376,37 +2376,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>224361</v>
+        <v>103023</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gräsberg, Hl</t>
+          <t>Björkasjö, Hl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>354051</v>
+        <v>354125</v>
       </c>
       <c r="R17" t="n">
-        <v>6331948</v>
+        <v>6332040</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2430,22 +2430,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2460,27 +2460,27 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Sindy Gullberg</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Sindy Gullberg</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136192690</t>
+          <t>https://artportalen.se/Sighting/136125410</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136192731</v>
+        <v>136192690</v>
       </c>
       <c r="B18" t="n">
-        <v>81112</v>
+        <v>98157</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2488,21 +2488,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>230185</v>
+        <v>224361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2583,16 +2583,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136192731</t>
+          <t>https://artportalen.se/Sighting/136192690</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136192963</v>
+        <v>136192731</v>
       </c>
       <c r="B19" t="n">
-        <v>81112</v>
+        <v>81113</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,13 +2624,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>354093</v>
+        <v>354051</v>
       </c>
       <c r="R19" t="n">
-        <v>6332012</v>
+        <v>6331948</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2694,6 +2694,118 @@
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136192731</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136192963</v>
+      </c>
+      <c r="B20" t="n">
+        <v>81113</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Gräsberg, Hl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>354093</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6332012</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Köinge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136192963</t>
         </is>
@@ -2719,6 +2831,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33477-2026 artfynd.xlsx
+++ b/artfynd/A 33477-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193005</v>
       </c>
       <c r="B2" t="n">
-        <v>96627</v>
+        <v>96638</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136194461</v>
       </c>
       <c r="B3" t="n">
-        <v>96627</v>
+        <v>96638</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136192933</v>
       </c>
       <c r="B4" t="n">
-        <v>77956</v>
+        <v>77960</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136193523</v>
       </c>
       <c r="B5" t="n">
-        <v>81126</v>
+        <v>81130</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136194440</v>
       </c>
       <c r="B6" t="n">
-        <v>77845</v>
+        <v>77849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136320537</v>
       </c>
       <c r="B7" t="n">
-        <v>81283</v>
+        <v>81287</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136125419</v>
       </c>
       <c r="B8" t="n">
-        <v>97967</v>
+        <v>97978</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136193996</v>
       </c>
       <c r="B9" t="n">
-        <v>96617</v>
+        <v>96628</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136125421</v>
       </c>
       <c r="B10" t="n">
-        <v>96606</v>
+        <v>96617</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>136193735</v>
       </c>
       <c r="B11" t="n">
-        <v>96606</v>
+        <v>96617</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136193984</v>
       </c>
       <c r="B12" t="n">
-        <v>96606</v>
+        <v>96617</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136125420</v>
       </c>
       <c r="B13" t="n">
-        <v>96411</v>
+        <v>96422</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>136193836</v>
       </c>
       <c r="B14" t="n">
-        <v>96411</v>
+        <v>96422</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136194444</v>
       </c>
       <c r="B15" t="n">
-        <v>79706</v>
+        <v>79710</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>136192690</v>
       </c>
       <c r="B18" t="n">
-        <v>98157</v>
+        <v>98168</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136192731</v>
       </c>
       <c r="B19" t="n">
-        <v>81113</v>
+        <v>81117</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>136192963</v>
       </c>
       <c r="B20" t="n">
-        <v>81113</v>
+        <v>81117</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 33477-2026 artfynd.xlsx
+++ b/artfynd/A 33477-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193005</v>
       </c>
       <c r="B2" t="n">
-        <v>96638</v>
+        <v>96651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136194461</v>
       </c>
       <c r="B3" t="n">
-        <v>96638</v>
+        <v>96651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136192933</v>
       </c>
       <c r="B4" t="n">
-        <v>77960</v>
+        <v>77966</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136193523</v>
       </c>
       <c r="B5" t="n">
-        <v>81130</v>
+        <v>81136</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136194440</v>
       </c>
       <c r="B6" t="n">
-        <v>77849</v>
+        <v>77855</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136320537</v>
       </c>
       <c r="B7" t="n">
-        <v>81287</v>
+        <v>81293</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136125419</v>
       </c>
       <c r="B8" t="n">
-        <v>97978</v>
+        <v>97991</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136193996</v>
       </c>
       <c r="B9" t="n">
-        <v>96628</v>
+        <v>96641</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136125421</v>
       </c>
       <c r="B10" t="n">
-        <v>96617</v>
+        <v>96630</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>136193735</v>
       </c>
       <c r="B11" t="n">
-        <v>96617</v>
+        <v>96630</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136193984</v>
       </c>
       <c r="B12" t="n">
-        <v>96617</v>
+        <v>96630</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136125420</v>
       </c>
       <c r="B13" t="n">
-        <v>96422</v>
+        <v>96435</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>136193836</v>
       </c>
       <c r="B14" t="n">
-        <v>96422</v>
+        <v>96435</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136194444</v>
       </c>
       <c r="B15" t="n">
-        <v>79710</v>
+        <v>79716</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136125414</v>
       </c>
       <c r="B16" t="n">
-        <v>58147</v>
+        <v>58152</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>136125410</v>
       </c>
       <c r="B17" t="n">
-        <v>58144</v>
+        <v>58149</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>136192690</v>
       </c>
       <c r="B18" t="n">
-        <v>98168</v>
+        <v>98181</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136192731</v>
       </c>
       <c r="B19" t="n">
-        <v>81117</v>
+        <v>81123</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>136192963</v>
       </c>
       <c r="B20" t="n">
-        <v>81117</v>
+        <v>81123</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 33477-2026 artfynd.xlsx
+++ b/artfynd/A 33477-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193005</v>
       </c>
       <c r="B2" t="n">
-        <v>96651</v>
+        <v>96652</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136194461</v>
       </c>
       <c r="B3" t="n">
-        <v>96651</v>
+        <v>96652</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136125419</v>
       </c>
       <c r="B8" t="n">
-        <v>97991</v>
+        <v>97992</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136193996</v>
       </c>
       <c r="B9" t="n">
-        <v>96641</v>
+        <v>96642</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136125421</v>
       </c>
       <c r="B10" t="n">
-        <v>96630</v>
+        <v>96631</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>136193735</v>
       </c>
       <c r="B11" t="n">
-        <v>96630</v>
+        <v>96631</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136193984</v>
       </c>
       <c r="B12" t="n">
-        <v>96630</v>
+        <v>96631</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136125420</v>
       </c>
       <c r="B13" t="n">
-        <v>96435</v>
+        <v>96436</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>136193836</v>
       </c>
       <c r="B14" t="n">
-        <v>96435</v>
+        <v>96436</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>136192690</v>
       </c>
       <c r="B18" t="n">
-        <v>98181</v>
+        <v>98182</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 33477-2026 artfynd.xlsx
+++ b/artfynd/A 33477-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193005</v>
       </c>
       <c r="B2" t="n">
-        <v>96652</v>
+        <v>96665</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136194461</v>
       </c>
       <c r="B3" t="n">
-        <v>96652</v>
+        <v>96665</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136192933</v>
       </c>
       <c r="B4" t="n">
-        <v>77966</v>
+        <v>77979</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136193523</v>
       </c>
       <c r="B5" t="n">
-        <v>81136</v>
+        <v>81149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136194440</v>
       </c>
       <c r="B6" t="n">
-        <v>77855</v>
+        <v>77868</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136320537</v>
       </c>
       <c r="B7" t="n">
-        <v>81293</v>
+        <v>81306</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136125419</v>
       </c>
       <c r="B8" t="n">
-        <v>97992</v>
+        <v>98005</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136193996</v>
       </c>
       <c r="B9" t="n">
-        <v>96642</v>
+        <v>96655</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136125421</v>
       </c>
       <c r="B10" t="n">
-        <v>96631</v>
+        <v>96644</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>136193735</v>
       </c>
       <c r="B11" t="n">
-        <v>96631</v>
+        <v>96644</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136193984</v>
       </c>
       <c r="B12" t="n">
-        <v>96631</v>
+        <v>96644</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136125420</v>
       </c>
       <c r="B13" t="n">
-        <v>96436</v>
+        <v>96449</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>136193836</v>
       </c>
       <c r="B14" t="n">
-        <v>96436</v>
+        <v>96449</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136194444</v>
       </c>
       <c r="B15" t="n">
-        <v>79716</v>
+        <v>79729</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136125414</v>
       </c>
       <c r="B16" t="n">
-        <v>58152</v>
+        <v>58165</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>136125410</v>
       </c>
       <c r="B17" t="n">
-        <v>58149</v>
+        <v>58162</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>136192690</v>
       </c>
       <c r="B18" t="n">
-        <v>98182</v>
+        <v>98195</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136192731</v>
       </c>
       <c r="B19" t="n">
-        <v>81123</v>
+        <v>81136</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>136192963</v>
       </c>
       <c r="B20" t="n">
-        <v>81123</v>
+        <v>81136</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 33477-2026 artfynd.xlsx
+++ b/artfynd/A 33477-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193005</v>
       </c>
       <c r="B2" t="n">
-        <v>96665</v>
+        <v>96666</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136194461</v>
       </c>
       <c r="B3" t="n">
-        <v>96665</v>
+        <v>96666</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136192933</v>
       </c>
       <c r="B4" t="n">
-        <v>77979</v>
+        <v>77980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136193523</v>
       </c>
       <c r="B5" t="n">
-        <v>81149</v>
+        <v>81150</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136194440</v>
       </c>
       <c r="B6" t="n">
-        <v>77868</v>
+        <v>77869</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136320537</v>
       </c>
       <c r="B7" t="n">
-        <v>81306</v>
+        <v>81307</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136125419</v>
       </c>
       <c r="B8" t="n">
-        <v>98005</v>
+        <v>98006</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136193996</v>
       </c>
       <c r="B9" t="n">
-        <v>96655</v>
+        <v>96656</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136125421</v>
       </c>
       <c r="B10" t="n">
-        <v>96644</v>
+        <v>96645</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>136193735</v>
       </c>
       <c r="B11" t="n">
-        <v>96644</v>
+        <v>96645</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136193984</v>
       </c>
       <c r="B12" t="n">
-        <v>96644</v>
+        <v>96645</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136125420</v>
       </c>
       <c r="B13" t="n">
-        <v>96449</v>
+        <v>96450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>136193836</v>
       </c>
       <c r="B14" t="n">
-        <v>96449</v>
+        <v>96450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136194444</v>
       </c>
       <c r="B15" t="n">
-        <v>79729</v>
+        <v>79730</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>136192690</v>
       </c>
       <c r="B18" t="n">
-        <v>98195</v>
+        <v>98196</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136192731</v>
       </c>
       <c r="B19" t="n">
-        <v>81136</v>
+        <v>81137</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>136192963</v>
       </c>
       <c r="B20" t="n">
-        <v>81136</v>
+        <v>81137</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
